--- a/purchase_order_request_forms/017_library_bookcases_requisition_form--purchase_order_request_forms.xlsx
+++ b/purchase_order_request_forms/017_library_bookcases_requisition_form--purchase_order_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Library Case Type</t>
+          <t>Library Case Type 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Item Quantity</t>
+          <t>Item 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Delivery Date</t>
+          <t>Delivery Date 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Delivery Time</t>
+          <t>Delivery Time 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Notes 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Shipping Address</t>
+          <t>Shipping Address 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Department 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Library Case Type</t>
+          <t>Library Case 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1056,8 +1056,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'1-3',_'value':_'1-3'}</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '1-3', 'value': '1-3'}</t>
+          <t>1-3</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'4-6',_'value':_'4-6'}</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '4-6', 'value': '4-6'}</t>
+          <t>4-6</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'7-12',_'value':_'7-12'}</t>
+          <t>7-12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '7-12', 'value': '7-12'}</t>
+          <t>7-12</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'13-20',_'value':_'13-20'}</t>
+          <t>13-20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '13-20', 'value': '13-20'}</t>
+          <t>13-20</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'1-3',_'value':_'1-3'}</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '1-3', 'value': '1-3'}</t>
+          <t>1-3</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'4-6',_'value':_'4-6'}</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '4-6', 'value': '4-6'}</t>
+          <t>4-6</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'7-12',_'value':_'7-12'}</t>
+          <t>7-12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '7-12', 'value': '7-12'}</t>
+          <t>7-12</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'13-20',_'value':_'13-20'}</t>
+          <t>13-20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '13-20', 'value': '13-20'}</t>
+          <t>13-20</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'1-3',_'value':_'1-3'}</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '1-3', 'value': '1-3'}</t>
+          <t>1-3</t>
         </is>
       </c>
     </row>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'4-6',_'value':_'4-6'}</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '4-6', 'value': '4-6'}</t>
+          <t>4-6</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'7-12',_'value':_'7-12'}</t>
+          <t>7-12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '7-12', 'value': '7-12'}</t>
+          <t>7-12</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'13-20',_'value':_'13-20'}</t>
+          <t>13-20</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '13-20', 'value': '13-20'}</t>
+          <t>13-20</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
